--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationrequest.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -648,7 +648,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -742,7 +742,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1012,7 +1012,7 @@
     <t>薬剤が投与あるいはその他の用途で利用されると想定される場面についての区分である。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCategory_VS|1.1.0a</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -1074,7 +1074,7 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Practitioner|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|PractitionerRole|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|RelatedPerson|4.0.1|Organization|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1109,7 +1109,7 @@
     <t>処方する製剤を表すコード。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1136,7 +1136,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1171,7 +1171,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1200,7 +1200,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1250,7 +1250,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1270,7 +1270,7 @@
     <t>MedicationRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson|CareTeam)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|RelatedPerson|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1301,7 +1301,7 @@
     <t>Performerを示さずにこのエレメントが指定された場合は、このエレメントは薬剤の投与／管理が指定の職種でなければならないと言うことを示している。Performerと共に指定された場合は、もし指定されたPerformerが実施できない場合に薬剤投与・管理を行うものについての要件が示されたことを意味する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS|1.1.0</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1313,7 +1313,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1367,7 +1367,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1420,7 +1420,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|1.3.0-dev|MedicationRequest|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|ServiceRequest|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|1.3.0-dev|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1469,7 +1469,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -1478,7 +1478,7 @@
     <t>MedicationRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Coverage|1.3.0-dev|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1522,7 +1522,7 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1584,7 +1584,7 @@
     <t>instructionForDispense</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_InstructionForDispense}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_InstructionForDispense|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1604,7 +1604,7 @@
     <t>expectedRepeatCount</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_ExpectedRepeatCount}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_ExpectedRepeatCount|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1659,7 +1659,7 @@
     <t>MedicationRequest.dispenseRequest.initialFill.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1980,7 +1980,7 @@
     <t>MedicationRequest.dispenseRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -2027,7 +2027,7 @@
     <t>代替品が許可されるかどうかは無視できないので、このエレメントはmodifierとしてラベルされる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionNotAllowedReason_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionNotAllowedReason_VS|1.1.0a</t>
   </si>
   <si>
     <t>code</t>
@@ -2051,7 +2051,7 @@
     <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
   </si>
   <si>
     <t>not mapped</t>
@@ -2066,7 +2066,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2089,7 +2089,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2441,7 +2441,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2456,7 +2456,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.26171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationrequest.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -648,7 +648,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -742,7 +742,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1012,7 +1012,7 @@
     <t>薬剤が投与あるいはその他の用途で利用されると想定される場面についての区分である。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCategory_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCategory_VS</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -1074,7 +1074,7 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Practitioner|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|PractitionerRole|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|RelatedPerson|4.0.1|Organization|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1109,7 +1109,7 @@
     <t>処方する製剤を表すコード。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1136,7 +1136,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1171,7 +1171,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1200,7 +1200,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1250,7 +1250,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>
@@ -1270,7 +1270,7 @@
     <t>MedicationRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|RelatedPerson|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson|CareTeam)
 </t>
   </si>
   <si>
@@ -1301,7 +1301,7 @@
     <t>Performerを示さずにこのエレメントが指定された場合は、このエレメントは薬剤の投与／管理が指定の職種でなければならないと言うことを示している。Performerと共に指定された場合は、もし指定されたPerformerが実施できない場合に薬剤投与・管理を行うものについての要件が示されたことを意味する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1313,7 +1313,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1367,7 +1367,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
 </t>
   </si>
   <si>
@@ -1420,7 +1420,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|1.3.0-dev|MedicationRequest|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|ServiceRequest|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|1.3.0-dev|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1469,7 +1469,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -1478,7 +1478,7 @@
     <t>MedicationRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Coverage|1.3.0-dev|ClaimResponse|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Coverage|ClaimResponse)
 </t>
   </si>
   <si>
@@ -1522,7 +1522,7 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage|1.3.0-dev}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage}
 </t>
   </si>
   <si>
@@ -1584,7 +1584,7 @@
     <t>instructionForDispense</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_InstructionForDispense|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_InstructionForDispense}
 </t>
   </si>
   <si>
@@ -1604,7 +1604,7 @@
     <t>expectedRepeatCount</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_ExpectedRepeatCount|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DispenseRequest_ExpectedRepeatCount}
 </t>
   </si>
   <si>
@@ -1659,7 +1659,7 @@
     <t>MedicationRequest.dispenseRequest.initialFill.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1980,7 +1980,7 @@
     <t>MedicationRequest.dispenseRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -2027,7 +2027,7 @@
     <t>代替品が許可されるかどうかは無視できないので、このエレメントはmodifierとしてラベルされる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionNotAllowedReason_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionNotAllowedReason_VS</t>
   </si>
   <si>
     <t>code</t>
@@ -2051,7 +2051,7 @@
     <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
   </si>
   <si>
     <t>not mapped</t>
@@ -2066,7 +2066,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest)
 </t>
   </si>
   <si>
@@ -2089,7 +2089,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
+    <t xml:space="preserve">Reference(DetectedIssue)
 </t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -2441,7 +2441,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2456,7 +2456,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.26171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
